--- a/HomeHelp_WorkerApp_Handoff.xlsx
+++ b/HomeHelp_WorkerApp_Handoff.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -156,6 +156,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1409,23 +1412,24 @@
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>- Request withdrawal
-- Money transferred to bank
-- Status Pending -&gt; Paid on real transfer</t>
-        </is>
-      </c>
-      <c r="F26" s="10" t="inlineStr">
-        <is>
-          <t>Pending</t>
+- Money transferred to bank via RazorpayX
+- Status Processing -&gt; Paid on real transfer
+- Failed payout auto-refunds to balance</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>GAP: ledger-only (Pending/Paid). No real bank payout (Razorpay Payouts) integrated.</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>DONE: RazorpayX payouts wired (contact -&gt; fund account -&gt; payout, bank/UPI) with webhook + ledger hold/withdraw/refund. Verified E2E in mock mode (success, idempotency, failure-refund). Add live keys (razorpay_key_id/secret, razorpayx_account_number, payout_mode, payout_webhook_secret) in Admin &gt; Settings to move real money. NOTE: bank penny-drop verification still manual.</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1729,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Worker App - Pending Gaps (assign to employees)</t>
         </is>
@@ -1838,9 +1842,9 @@
           <t>Real worker payouts</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1850,12 +1854,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Integrate Razorpay Payouts (or bank transfer) for withdrawals; status Pending -&gt; Paid on real transfer + webhook.</t>
+          <t>DONE — RazorpayX payouts integrated (contact/fund-account/payout, bank + UPI), webhook, ledger hold/withdraw/refund, mock fallback. Just add live keys in Admin &gt; Settings.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>A withdrawal moves real money to the bank and marks Paid via webhook.</t>
+          <t>A withdrawal moves real money to the bank and marks Paid via webhook. [Verified E2E in mock mode]</t>
         </is>
       </c>
     </row>

--- a/HomeHelp_WorkerApp_Handoff.xlsx
+++ b/HomeHelp_WorkerApp_Handoff.xlsx
@@ -51,11 +51,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D97706"/>
+      <color rgb="00DC2626"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00DC2626"/>
+      <color rgb="00D97706"/>
     </font>
     <font>
       <color rgb="006B7280"/>
@@ -90,12 +90,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,19 +146,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -681,39 +681,40 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Bank details</t>
+          <t>Bank details + verification</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Add/update payout bank account + status.</t>
+          <t>Add/update payout bank account; auto-verified.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>As a worker, I want to add my bank details so I can receive payouts.</t>
+          <t>As a worker, I want to add my bank details and have them verified so payouts reach the right account.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>- Save bank + status
-- Shows verification status
+          <t>- Save bank / UPI
+- Auto penny-drop verification (RazorpayX)
+- Account + registered-name checked; status Verified/Rejected
 - Used by payout</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Partial</t>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Completed</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Stored, but real payout not integrated (see Payouts).</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>DONE: RazorpayX Fund Account Validation (penny-drop) on save -&gt; auto Verified/Rejected with bank's registered name + name-match flag; async webhook; replaces manual admin approval. Mock auto-verify when keys absent. Verified E2E. Live check needs RazorpayX keys + fund_account.validation webhook.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Passed</t>
         </is>
       </c>
     </row>
@@ -742,7 +743,7 @@
 - Status shown to worker</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -752,7 +753,7 @@
           <t>GAP: backend stores only a filename string, not the file. No cloud storage; admin cannot view the image.</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -822,7 +823,7 @@
 - On-shift drives auto-assign</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -832,7 +833,7 @@
           <t>Endpoint exists; demand-based slot opening (Snabbit-style) not built. Admin still rosters manually.</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -868,7 +869,7 @@
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -904,7 +905,7 @@
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -938,7 +939,7 @@
 - Tapping opens the job</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -948,7 +949,7 @@
           <t>GAP: currently an 8s polling foreground service; NO FCM. No wake-from-killed; battery drain.</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -983,7 +984,7 @@
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1019,7 +1020,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1054,7 +1055,7 @@
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1089,7 +1090,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1124,7 +1125,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1154,7 +1155,7 @@
 - Ledger updated</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1164,7 +1165,7 @@
           <t>Wired; needs end-to-end verification with a real completed cash booking.</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -1199,7 +1200,7 @@
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1232,7 +1233,7 @@
 - Route/navigation</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
@@ -1242,7 +1243,7 @@
           <t>GAP: Google Maps key is a placeholder (YOUR_API_KEY_HERE); falls back to OSM map. Add a real key or standardize on OSM.</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -1277,7 +1278,7 @@
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1316,7 +1317,7 @@
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1351,7 +1352,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1386,7 +1387,7 @@
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1427,7 +1428,7 @@
           <t>DONE: RazorpayX payouts wired (contact -&gt; fund account -&gt; payout, bank/UPI) with webhook + ledger hold/withdraw/refund. Verified E2E in mock mode (success, idempotency, failure-refund). Add live keys (razorpay_key_id/secret, razorpayx_account_number, payout_mode, payout_webhook_secret) in Admin &gt; Settings to move real money. NOTE: bank penny-drop verification still manual.</t>
         </is>
       </c>
-      <c r="H26" s="12" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
@@ -1460,7 +1461,7 @@
 - Server sends push on events</t>
         </is>
       </c>
-      <c r="F27" s="10" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -1470,7 +1471,7 @@
           <t>GAP: no FCM (same root as job alerts). Only in-app/polling now.</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -1505,7 +1506,7 @@
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1544,7 +1545,7 @@
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1583,7 +1584,7 @@
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1622,7 +1623,7 @@
           <t>Endpoints present; verify claim flow.</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1657,7 +1658,7 @@
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1696,7 +1697,7 @@
           <t>i18n present.</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>Not Tested</t>
         </is>
@@ -1778,7 +1779,7 @@
           <t>Real-time job alerts (FCM)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1810,7 +1811,7 @@
           <t>KYC document storage</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1874,7 +1875,7 @@
           <t>Google Maps key</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1906,7 +1907,7 @@
           <t>Cash settlement E2E</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1938,7 +1939,7 @@
           <t>Live OTP (SMS)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1970,7 +1971,7 @@
           <t>Customer payments (Razorpay)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
